--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -755,14 +755,26 @@
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>16/10/2027</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
     </row>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16/10/2027</t>
+          <t>16/12/2027</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,15 +768,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16/12/2027</t>
+          <t>16/02/2029</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16/02/2029</t>
+          <t>16/03/2027</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16/03/2027</t>
+          <t>16/02/2027</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16/02/2027</t>
+          <t>16/01/2027</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16/01/2027</t>
+          <t>16/12/2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AUA</t>
+          <t>Prova antincendio annuale</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TUA 151</t>
+          <t>Legge 81/08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AUA</t>
+          <t>Verbale avenuta prova antincedio</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -480,16 +480,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03/09/2027</t>
+          <t>03/04/2027</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RSA</t>
+          <t>RSSL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -497,17 +497,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCIA</t>
+          <t>Prova emergenza annuale</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Legge 81/08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Verbale prova emergenza</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -516,30 +516,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>09/07/2027</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RSSL</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Verifica dei presidi antincendio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>D.P.R. 26/5/59 n°689
+D.M. 10/3/98
+DPR 151/11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Registro Verifica</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -548,247 +554,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11/03/2027</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>11/11/2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RSSL</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Altro</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>inventato</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>23/12/2026</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>nuovo</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>plot</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>tufo</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>16/08/2026</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>prova</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tu</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>12/03/2027</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>20p</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Esempio</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>05/07/2027</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Prova 2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>30/07/2026</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>12</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>30/07/2027</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>16/12/2026</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,16 +569,100 @@
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Squadra antincendio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Legge 81/08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Attestati Formazione</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>16/10/2024</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16/10/2029</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Squadra primo soccorso</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Legge 81/08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Attestati Formazione</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>36</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12/12/2028</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Schede di sicurezza - Agenti Chimici</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Legge 81/08 e REACH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Schede di sicurezza</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>27/02/2027</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
